--- a/src/test/resources/testdata/Modules/04_Redemptions/Redemptions/05_AddRedemptionTest.xlsx
+++ b/src/test/resources/testdata/Modules/04_Redemptions/Redemptions/05_AddRedemptionTest.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\04_Redemptions\Redemptions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B40E32C2-4E82-4409-BEE2-7B562D093CD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{199AA9B5-58A4-4103-A845-D38DD85282BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="126">
   <si>
     <t>TESTCASE_ID</t>
   </si>
@@ -54,12 +55,6 @@
   </si>
   <si>
     <t>MODULE_NAME</t>
-  </si>
-  <si>
-    <t>FROM_DATE</t>
-  </si>
-  <si>
-    <t>TO_DATE</t>
   </si>
   <si>
     <t>2602000005</t>
@@ -367,7 +362,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">TDS % </t>
+      <t>TDS Points value</t>
     </r>
     <r>
       <rPr>
@@ -381,6 +376,880 @@
   </si>
   <si>
     <r>
+      <t>Verify after click on</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Downlod pdf button</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Download started</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">" </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>toast</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> should </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>appears</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> on screen.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">After click on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cancel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>button</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> navigate to</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> dashboard page</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>AddRedemptionTest_01</t>
+  </si>
+  <si>
+    <t>AddRedemptionTest_02</t>
+  </si>
+  <si>
+    <t>AddRedemptionTest_03</t>
+  </si>
+  <si>
+    <t>AddRedemptionTest_04</t>
+  </si>
+  <si>
+    <t>AddRedemptionTest_05</t>
+  </si>
+  <si>
+    <t>AddRedemptionTest_06</t>
+  </si>
+  <si>
+    <t>AddRedemptionTest_07</t>
+  </si>
+  <si>
+    <t>AddRedemptionTest_08</t>
+  </si>
+  <si>
+    <t>AddRedemptionTest_09</t>
+  </si>
+  <si>
+    <t>AddRedemptionTest_10</t>
+  </si>
+  <si>
+    <t>AddRedemptionTest_11</t>
+  </si>
+  <si>
+    <t>AddRedemptionTest_12</t>
+  </si>
+  <si>
+    <t>AddRedemptionTest_13</t>
+  </si>
+  <si>
+    <t>AddRedemptionTest_14</t>
+  </si>
+  <si>
+    <t>AddRedemptionTest_15</t>
+  </si>
+  <si>
+    <t>AddRedemptionTest_16</t>
+  </si>
+  <si>
+    <t>AddRedemptionTest_17</t>
+  </si>
+  <si>
+    <t>AddRedemptionTest_18</t>
+  </si>
+  <si>
+    <t>AddRedemptionTest_19</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">After enter </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Valid OTP &amp; Verify</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, then redemption should be add and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Redemption Submitted successfully</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> pop-up should be show.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">After </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Submit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Redemption</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> User should navigate to " </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Redemption Details Page</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Verify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Added Redemption</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> should be </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>show</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Redemption History Pending</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tab.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Verify Added Redemption</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  on Redemption History</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Pending</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tab.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Verify Added Redemption</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Product code</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  on Redemption History</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Pending</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tab.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Verify Added Redemption</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Product Desc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  on Redemption History</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Pending</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tab.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Verify Added Redemption</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> QTY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  on Redemption History</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Pending</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tab.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Verify Added Redemption</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Total Points</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  on Redemption History</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Pending</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tab.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Verify Added Redemption</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> TDS Points value</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  on Redemption History</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Pending</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tab.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Verify Added Redemption</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Total Redeem Points</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  on Redemption History</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Pending</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tab.</t>
+    </r>
+  </si>
+  <si>
+    <t>AddRedemptionTest_20</t>
+  </si>
+  <si>
+    <t>AddRedemptionTest_21</t>
+  </si>
+  <si>
+    <t>AddRedemptionTest_22</t>
+  </si>
+  <si>
+    <t>AddRedemptionTest_23</t>
+  </si>
+  <si>
+    <t>AddRedemptionTest_24</t>
+  </si>
+  <si>
+    <t>AddRedemptionTest_25</t>
+  </si>
+  <si>
+    <t>AddRedemptionTest_26</t>
+  </si>
+  <si>
+    <t>AddRedemptionTest_27</t>
+  </si>
+  <si>
+    <t>TEST_DESC</t>
+  </si>
+  <si>
+    <t>SEARCH_DATA</t>
+  </si>
+  <si>
+    <t>QTY</t>
+  </si>
+  <si>
+    <t>ABMPL213973</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>DELIVERED_ADDRESS</t>
+  </si>
+  <si>
+    <t>PINCODE</t>
+  </si>
+  <si>
+    <t>DISTRICT</t>
+  </si>
+  <si>
+    <t>PAN_NUMBER</t>
+  </si>
+  <si>
+    <t>Mayur Colony, Kothrud, Pune</t>
+  </si>
+  <si>
+    <t>411038</t>
+  </si>
+  <si>
+    <t>Pune</t>
+  </si>
+  <si>
+    <t>ADGFS9876D</t>
+  </si>
+  <si>
+    <t>OTP</t>
+  </si>
+  <si>
+    <t>2222</t>
+  </si>
+  <si>
+    <t>summary_clickon_success_okbtn
+verifypagetitle</t>
+  </si>
+  <si>
+    <t>EXPECTED_KEY</t>
+  </si>
+  <si>
+    <t>SUMMARY_DELIVEREDADDRESS</t>
+  </si>
+  <si>
+    <t>SUMMARY_DELIVEREDMOBILENO</t>
+  </si>
+  <si>
+    <t>SUMMARY_PINCODE</t>
+  </si>
+  <si>
+    <t>SUMMARY_CITY</t>
+  </si>
+  <si>
+    <t>SUMMARY_STATE</t>
+  </si>
+  <si>
+    <t>SUMMARY_DISTRICT</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>verify_redemtiondetails_deliveredaddress</t>
+  </si>
+  <si>
+    <t>verify_redemtiondetails_deliveredmobileno</t>
+  </si>
+  <si>
+    <t>verify_redemtiondetails_pincode</t>
+  </si>
+  <si>
+    <t>verify_redemtiondetails_city</t>
+  </si>
+  <si>
+    <t>verify_redemtiondetails_state</t>
+  </si>
+  <si>
+    <t>verify_redemtiondetails_district</t>
+  </si>
+  <si>
+    <t>verify_redemtiondetails_redemptionno</t>
+  </si>
+  <si>
+    <t>verify_redemtiondetails_redemptiondate</t>
+  </si>
+  <si>
+    <t>CATALOGUE_PRODUCTDESC</t>
+  </si>
+  <si>
+    <t>CATALOGUE_POINTS</t>
+  </si>
+  <si>
+    <t>CATALOGUE_QTY</t>
+  </si>
+  <si>
+    <t>CATALOGIE_TDSPOINTS</t>
+  </si>
+  <si>
+    <t>verify_redemtiondetails_productcode</t>
+  </si>
+  <si>
+    <t>verify_redemtiondetails_productdesc</t>
+  </si>
+  <si>
+    <t>verify_redemtiondetails_productqty</t>
+  </si>
+  <si>
+    <t>verify_redemtiondetails_productpoints</t>
+  </si>
+  <si>
+    <t>verify_redemtiondetails_tdspoints</t>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">Verify  </t>
     </r>
     <r>
@@ -391,7 +1260,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>TDS Points value</t>
+      <t>Total Redeem Points</t>
     </r>
     <r>
       <rPr>
@@ -404,831 +1273,112 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Verify  </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Total Redeem Points</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> on Redemption Details</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Verify after click on</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Downlod pdf button</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> "</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Download started</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">" </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>toast</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> should </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>appears</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> on screen.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">After click on </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>cancel</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>button</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> navigate to</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> dashboard page</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>AddRedemptionTest_01</t>
-  </si>
-  <si>
-    <t>AddRedemptionTest_02</t>
-  </si>
-  <si>
-    <t>AddRedemptionTest_03</t>
-  </si>
-  <si>
-    <t>AddRedemptionTest_04</t>
-  </si>
-  <si>
-    <t>AddRedemptionTest_05</t>
-  </si>
-  <si>
-    <t>AddRedemptionTest_06</t>
-  </si>
-  <si>
-    <t>AddRedemptionTest_07</t>
-  </si>
-  <si>
-    <t>AddRedemptionTest_08</t>
-  </si>
-  <si>
-    <t>AddRedemptionTest_09</t>
-  </si>
-  <si>
-    <t>AddRedemptionTest_10</t>
-  </si>
-  <si>
-    <t>AddRedemptionTest_11</t>
-  </si>
-  <si>
-    <t>AddRedemptionTest_12</t>
-  </si>
-  <si>
-    <t>AddRedemptionTest_13</t>
-  </si>
-  <si>
-    <t>AddRedemptionTest_14</t>
-  </si>
-  <si>
-    <t>AddRedemptionTest_15</t>
-  </si>
-  <si>
-    <t>AddRedemptionTest_16</t>
-  </si>
-  <si>
-    <t>AddRedemptionTest_17</t>
-  </si>
-  <si>
-    <t>AddRedemptionTest_18</t>
-  </si>
-  <si>
-    <t>AddRedemptionTest_19</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">After enter </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Valid OTP &amp; Verify</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, then redemption should be add and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Redemption Submitted successfully</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> pop-up should be show.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">After </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Submit</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Redemption</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> User should navigate to " </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Redemption Details Page</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Verify </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Added Redemption</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> should be </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>show</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> on </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Redemption History Pending</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tab.</t>
-    </r>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <r>
-      <t>Verify Added Redemption</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> date</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  on Redemption History</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Pending</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tab.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Verify Added Redemption</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Product code</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  on Redemption History</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Pending</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tab.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Verify Added Redemption</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Product Desc</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  on Redemption History</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Pending</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tab.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Verify Added Redemption</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> QTY</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  on Redemption History</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Pending</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tab.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Verify Added Redemption</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Total Points</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  on Redemption History</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Pending</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tab.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Verify Added Redemption</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> TDS %</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  on Redemption History</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Pending</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tab.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Verify Added Redemption</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> TDS Points value</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  on Redemption History</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Pending</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tab.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Verify Added Redemption</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Total Redeem Points</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  on Redemption History</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Pending</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tab.</t>
-    </r>
-  </si>
-  <si>
-    <t>AddRedemptionTest_20</t>
-  </si>
-  <si>
-    <t>AddRedemptionTest_21</t>
-  </si>
-  <si>
-    <t>AddRedemptionTest_22</t>
-  </si>
-  <si>
-    <t>AddRedemptionTest_23</t>
-  </si>
-  <si>
-    <t>AddRedemptionTest_24</t>
-  </si>
-  <si>
-    <t>AddRedemptionTest_25</t>
-  </si>
-  <si>
-    <t>AddRedemptionTest_26</t>
-  </si>
-  <si>
-    <t>AddRedemptionTest_27</t>
-  </si>
-  <si>
-    <t>AddRedemptionTest_28</t>
+    <t>redemtiondetails_get_totalredeempoints
+verify_redemtiondetails_totalredeempoints_calculation</t>
+  </si>
+  <si>
+    <t>REDEMPTIONDETAILS_TOTALREDEEMPOINTS</t>
+  </si>
+  <si>
+    <t>redemtiondetails_clickon_downloadpdf
+verify_redemtiondetails_downloadstartedtext</t>
+  </si>
+  <si>
+    <t>redemtiondetails_get_redemptionno
+redemtiondetails_get_redemptiondate
+redemtiondetails_clickon_cancelbtn
+verify_navigatetodashboard</t>
+  </si>
+  <si>
+    <t>openredemptionsmenu
+verify_redhistory_redemptionno_present</t>
+  </si>
+  <si>
+    <t>verify_redhistory_generated_date</t>
+  </si>
+  <si>
+    <t>CONTAINS</t>
+  </si>
+  <si>
+    <t>GENERATED_REDEMPTIONDATE</t>
+  </si>
+  <si>
+    <t>verify_redhistory_generated_productcode</t>
+  </si>
+  <si>
+    <t>verify_redhistory_generated_productdesc</t>
+  </si>
+  <si>
+    <t>verify_redhistory_generated_qty</t>
+  </si>
+  <si>
+    <t>verify_redhistory_generated_totalpoints</t>
+  </si>
+  <si>
+    <t>verify_redhistory_generated_tdspoints</t>
+  </si>
+  <si>
+    <t>verify_redhistory_generated_totalredeempoints
+navigatebacktodashboardpage</t>
+  </si>
+  <si>
+    <t>Redemption Details</t>
+  </si>
+  <si>
+    <t>Success</t>
+  </si>
+  <si>
+    <t>openredemptionsmenu
+redhistory_clickon_fabbutton
+catalogue_enter_searchdata
+catalogue_clickon_keyboardsearchicon
+hidekeyboard
+catalogue_enter_qty
+hidekeyboard
+catalogue_get_rewardproductcode
+catalogue_get_rewardproductcode_bysplit
+catalogue_get_rewardproductdesc
+catalogue_get_rewardproductpoints
+catalogue_get_rewardproductqty
+catalogue_get_cartpoints
+catalogue_get_tdspoints
+catalogue_get_tdspercentage
+catalogue_clickon_submitbtn
+redemptioncart_clickon_checkoutbtn
+summary_enter_deliveredaddress
+summary_enter_pincode
+summary_enter_district
+summary_enter_panno
+summary_get_deliveredaddress
+summary_get_deliveredmobile
+summary_get_pincode
+summary_get_city
+summary_get_state
+summary_get_district
+summary_get_panno
+summary_clickon_checkout
+summary_clickon_declaration_acceptbtn
+summary_enter_otpverfy_otp
+summary_clickon_otpverfy_verifybtn
+verify_summary_success_title</t>
+  </si>
+  <si>
+    <t>CATALOGUE_PRODUCTCODE_PART</t>
+  </si>
+  <si>
+    <t>verify_summary_successy_text</t>
+  </si>
+  <si>
+    <t>2602000006</t>
+  </si>
+  <si>
+    <t>2602000007</t>
+  </si>
+  <si>
+    <t>Verify Success Text on Success Dialog box</t>
+  </si>
+  <si>
+    <t>Redemption Request Submitted Successfully.</t>
   </si>
 </sst>
 </file>
@@ -1390,7 +1540,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1576,8 +1726,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1707,6 +1869,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1753,7 +1939,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1761,8 +1947,24 @@
     <xf numFmtId="49" fontId="18" fillId="0" borderId="10" xfId="42" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="13" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="13" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="33" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="35" borderId="10" xfId="42" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2139,585 +2341,1842 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{089D5808-B2AF-4105-BEF8-05FAA4CBE122}">
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.90625" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.7265625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.08984375" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="103.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="30.26953125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="20.81640625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="11.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.90625" style="2"/>
+    <col min="5" max="5" width="52.453125" style="2" customWidth="1"/>
+    <col min="6" max="12" width="30.26953125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="37.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="30.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.90625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E1" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" s="6" t="s">
+      <c r="F1" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="N1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="O1" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="409.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="M2" s="9"/>
+      <c r="N2" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F3" s="8"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="E5" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-    </row>
-    <row r="3" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-    </row>
-    <row r="4" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="1"/>
+      <c r="E6" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
-    </row>
-    <row r="7" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="1"/>
+        <v>11</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
-    </row>
-    <row r="8" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>88</v>
+      </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
-    </row>
-    <row r="9" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>89</v>
+      </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
-    </row>
-    <row r="10" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="1"/>
+        <v>14</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>90</v>
+      </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
-    </row>
-    <row r="11" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>10</v>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>8</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-    </row>
-    <row r="12" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="1"/>
+        <v>16</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
-    </row>
-    <row r="13" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>97</v>
+      </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
-    </row>
-    <row r="14" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" s="1"/>
+        <v>18</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>98</v>
+      </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
-    </row>
-    <row r="15" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="1"/>
+        <v>19</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>99</v>
+      </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
-    </row>
-    <row r="16" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" s="1"/>
+        <v>20</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
-    </row>
-    <row r="17" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
-    </row>
-    <row r="18" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>10</v>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A18" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>8</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-    </row>
-    <row r="19" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>105</v>
+      </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
-    </row>
-    <row r="20" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="58" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>106</v>
+      </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
-    </row>
-    <row r="21" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E21" s="1"/>
+        <v>45</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>107</v>
+      </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
-    </row>
-    <row r="22" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E22" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
-    </row>
-    <row r="23" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E23" s="1"/>
+        <v>47</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>111</v>
+      </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
-    </row>
-    <row r="24" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E24" s="1"/>
+        <v>48</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>112</v>
+      </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
-    </row>
-    <row r="25" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E25" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>113</v>
+      </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
-    </row>
-    <row r="26" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E26" s="1"/>
+        <v>50</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>114</v>
+      </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
-    </row>
-    <row r="27" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E27" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
-    </row>
-    <row r="28" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E28" s="1"/>
+        <v>52</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>116</v>
+      </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
-    </row>
-    <row r="29" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{439B7AD1-4401-4554-B4EA-F630D6F33B8B}">
+  <dimension ref="A1:O28"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="20.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="103.26953125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="52.453125" style="2" customWidth="1"/>
+    <col min="6" max="12" width="30.26953125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="37.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="30.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.90625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="M2" s="9"/>
+      <c r="N2" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F3" s="8"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A18" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="58" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/test/resources/testdata/Modules/04_Redemptions/Redemptions/05_AddRedemptionTest.xlsx
+++ b/src/test/resources/testdata/Modules/04_Redemptions/Redemptions/05_AddRedemptionTest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\04_Redemptions\Redemptions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{199AA9B5-58A4-4103-A845-D38DD85282BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2CE75C-50EE-4650-811E-AEAE98CBF31F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -2450,7 +2450,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>122</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>8</v>
@@ -2481,7 +2481,7 @@
     </row>
     <row r="4" spans="1:15" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>123</v>
+        <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>8</v>
@@ -2697,7 +2697,7 @@
       </c>
     </row>
     <row r="11" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B11" s="9" t="s">
@@ -2914,7 +2914,7 @@
       </c>
     </row>
     <row r="18" spans="1:15" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B18" s="9" t="s">
